--- a/data/trans_orig/P05A04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A04-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2007</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2007 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>420365</t>
+          <t>419350</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>448893</t>
+          <t>448585</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>401117</t>
+          <t>397972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>424700</t>
+          <t>424523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>830310</t>
+          <t>824871</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>868654</t>
+          <t>864697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33761</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59931</t>
+          <t>59724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +861,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>36810</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>27463</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>49453</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>81655</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>65658</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>100203</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>6,9%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>36810</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>27592</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>49120</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>81655</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>98672</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13697</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32367</t>
+          <t>33185</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>646502</t>
+          <t>645667</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>677382</t>
+          <t>677932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>525890</t>
+          <t>525203</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>558707</t>
+          <t>560612</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1182608</t>
+          <t>1182833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1229969</t>
+          <t>1230836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37323</t>
+          <t>36951</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65490</t>
+          <t>64337</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42437</t>
+          <t>40316</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71828</t>
+          <t>72441</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>84066</t>
+          <t>85249</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>127532</t>
+          <t>126123</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28270</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>18979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41714</t>
+          <t>43485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>526236</t>
+          <t>529034</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>562274</t>
+          <t>563734</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>601557</t>
+          <t>602204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>631547</t>
+          <t>632442</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1141374</t>
+          <t>1138444</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1188523</t>
+          <t>1188114</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,94%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60969</t>
+          <t>61496</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96115</t>
+          <t>93806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43291</t>
+          <t>43542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71127</t>
+          <t>71537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110444</t>
+          <t>110462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154539</t>
+          <t>158739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15261</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36093</t>
+          <t>34986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>452507</t>
+          <t>452385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>479560</t>
+          <t>478301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>434855</t>
+          <t>436712</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>464498</t>
+          <t>464829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>895730</t>
+          <t>897088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>936295</t>
+          <t>935467</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27235</t>
+          <t>26715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50891</t>
+          <t>50025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39569</t>
+          <t>38204</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66412</t>
+          <t>65076</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71108</t>
+          <t>73602</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108731</t>
+          <t>109493</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15507</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28985</t>
+          <t>29418</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>315088</t>
+          <t>315475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>340450</t>
+          <t>341108</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>343305</t>
+          <t>344383</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368306</t>
+          <t>368836</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>664609</t>
+          <t>665943</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>703379</t>
+          <t>701697</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33377</t>
+          <t>33327</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>58408</t>
+          <t>57337</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19595</t>
+          <t>20735</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41349</t>
+          <t>41029</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>58739</t>
+          <t>59332</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92243</t>
+          <t>92801</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>14888</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22423</t>
+          <t>23034</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14445</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33471</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>255095</t>
+          <t>253962</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>274565</t>
+          <t>272700</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>293283</t>
+          <t>295254</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>316371</t>
+          <t>316580</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>556857</t>
+          <t>556741</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>585424</t>
+          <t>584931</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29615</t>
+          <t>30233</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40321</t>
+          <t>39205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37246</t>
+          <t>37441</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63104</t>
+          <t>62382</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>13494</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>181040</t>
+          <t>181267</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>196560</t>
+          <t>195923</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>281370</t>
+          <t>280954</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>305766</t>
+          <t>306113</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>470486</t>
+          <t>470423</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>498411</t>
+          <t>497885</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24492</t>
+          <t>23732</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21377</t>
+          <t>21239</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45283</t>
+          <t>45693</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34460</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62212</t>
+          <t>62135</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2861751</t>
+          <t>2859621</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2930246</t>
+          <t>2929945</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2952014</t>
+          <t>2949403</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3023578</t>
+          <t>3023021</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5833325</t>
+          <t>5833430</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5936848</t>
+          <t>5931113</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>259211</t>
+          <t>256541</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>320905</t>
+          <t>326232</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>251516</t>
+          <t>256036</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>320428</t>
+          <t>321217</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526663</t>
+          <t>533690</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>623516</t>
+          <t>626340</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>75171</t>
+          <t>77251</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>56691</t>
+          <t>56876</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>92720</t>
+          <t>90920</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>107483</t>
+          <t>109209</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>156963</t>
+          <t>154712</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2012</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2012 (tasa de respuesta: 99,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>394678</t>
+          <t>395629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>416571</t>
+          <t>417598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>388403</t>
+          <t>388519</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>409611</t>
+          <t>409490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>791284</t>
+          <t>791922</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>821853</t>
+          <t>821182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25129</t>
+          <t>24224</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45677</t>
+          <t>44892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29567</t>
+          <t>29106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39773</t>
+          <t>39346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67993</t>
+          <t>67009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,82 +4857,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>7026</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>14028</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>11888</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>6648</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>20842</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>2,39%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7026</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2983</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>14732</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>11888</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>6275</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>19965</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>609223</t>
+          <t>609078</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>639930</t>
+          <t>640031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>534484</t>
+          <t>535230</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>563663</t>
+          <t>563726</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1155365</t>
+          <t>1153361</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1195289</t>
+          <t>1196712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28740</t>
+          <t>29828</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54518</t>
+          <t>55614</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33229</t>
+          <t>32654</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59684</t>
+          <t>58693</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67377</t>
+          <t>66711</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>102347</t>
+          <t>105926</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>25889</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41384</t>
+          <t>39795</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>582554</t>
+          <t>581071</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>616402</t>
+          <t>616371</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>622064</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>652398</t>
+          <t>652571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1217659</t>
+          <t>1216474</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1262858</t>
+          <t>1263214</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41864</t>
+          <t>42991</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70562</t>
+          <t>71830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35891</t>
+          <t>36686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63744</t>
+          <t>64250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86650</t>
+          <t>85895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125310</t>
+          <t>126115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>32199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>24034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21793</t>
+          <t>21910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46486</t>
+          <t>46175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>531667</t>
+          <t>531602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>565372</t>
+          <t>564827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>534667</t>
+          <t>534879</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>564287</t>
+          <t>564770</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1077736</t>
+          <t>1077599</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1121257</t>
+          <t>1122939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34693</t>
+          <t>35105</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63618</t>
+          <t>64622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35194</t>
+          <t>34385</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62723</t>
+          <t>62978</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>77588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115989</t>
+          <t>116524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27018</t>
+          <t>27590</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>18190</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>39893</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>390095</t>
+          <t>389446</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>411659</t>
+          <t>411693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>385288</t>
+          <t>384889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>412005</t>
+          <t>412404</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>782202</t>
+          <t>784438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>817859</t>
+          <t>819075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32862</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22961</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46044</t>
+          <t>44559</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42013</t>
+          <t>40716</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71971</t>
+          <t>69853</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11968</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20837</t>
+          <t>21231</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>268665</t>
+          <t>270087</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>289165</t>
+          <t>289957</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>311401</t>
+          <t>313556</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>332370</t>
+          <t>332733</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>590818</t>
+          <t>588729</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>618793</t>
+          <t>617326</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11307</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30410</t>
+          <t>29081</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31341</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26915</t>
+          <t>28196</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51581</t>
+          <t>52537</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>11894</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>15131</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>19841</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>222601</t>
+          <t>225468</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>240233</t>
+          <t>240371</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>342669</t>
+          <t>342412</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>365775</t>
+          <t>365206</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>573007</t>
+          <t>572061</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>601588</t>
+          <t>601528</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20627</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19966</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42552</t>
+          <t>42083</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>28061</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55751</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3066346</t>
+          <t>3063336</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3135577</t>
+          <t>3131206</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3185672</t>
+          <t>3184442</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3254090</t>
+          <t>3254864</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6271932</t>
+          <t>6271385</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6368819</t>
+          <t>6367958</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>199968</t>
+          <t>199682</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>260202</t>
+          <t>264374</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>211171</t>
+          <t>210645</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>274378</t>
+          <t>273717</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>428126</t>
+          <t>433378</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>517208</t>
+          <t>518549</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>52871</t>
+          <t>55021</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>89074</t>
+          <t>89764</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>47863</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>79370</t>
+          <t>79311</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>107265</t>
+          <t>109538</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>154609</t>
+          <t>156782</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2016</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2016 (tasa de respuesta: 99,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>362830</t>
+          <t>362363</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>389897</t>
+          <t>388394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,82 +8514,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>86,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>93,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>346347</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>332202</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>358236</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>88,18%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>84,57%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>723540</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>704831</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>740556</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>89,38%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>87,07%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>346347</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>332340</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>357246</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>88,18%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>84,61%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>90,95%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>723540</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>705332</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>738879</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>89,38%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>87,13%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22594</t>
+          <t>22337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46680</t>
+          <t>46868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26474</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48657</t>
+          <t>50087</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55637</t>
+          <t>55015</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88866</t>
+          <t>87564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25573</t>
+          <t>25541</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493601</t>
+          <t>493013</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>527065</t>
+          <t>526710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482609</t>
+          <t>485082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510709</t>
+          <t>512286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>984881</t>
+          <t>986181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1031522</t>
+          <t>1029305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41427</t>
+          <t>41292</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70543</t>
+          <t>70817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31097</t>
+          <t>30499</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55532</t>
+          <t>54288</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78903</t>
+          <t>79240</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>116345</t>
+          <t>114831</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30394</t>
+          <t>28491</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32818</t>
+          <t>31070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28433</t>
+          <t>28300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54374</t>
+          <t>53861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>585079</t>
+          <t>586563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>617753</t>
+          <t>617301</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>576337</t>
+          <t>576737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>607506</t>
+          <t>605656</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1173650</t>
+          <t>1174347</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1217994</t>
+          <t>1217089</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37870</t>
+          <t>37953</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65609</t>
+          <t>66244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34314</t>
+          <t>34697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60437</t>
+          <t>60076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77673</t>
+          <t>78171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116052</t>
+          <t>116326</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19502</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25706</t>
+          <t>26881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>18729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39613</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>539838</t>
+          <t>541146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>574623</t>
+          <t>576279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>556650</t>
+          <t>557362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>588447</t>
+          <t>587666</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1108282</t>
+          <t>1108465</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1154681</t>
+          <t>1152572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41263</t>
+          <t>40548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72075</t>
+          <t>69787</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34654</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62082</t>
+          <t>61801</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85492</t>
+          <t>84661</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>126559</t>
+          <t>123042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13580</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34636</t>
+          <t>34035</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12657</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29850</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30518</t>
+          <t>30767</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57457</t>
+          <t>59213</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>403937</t>
+          <t>405140</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>433541</t>
+          <t>433193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>413259</t>
+          <t>411676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>444509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>825929</t>
+          <t>825305</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>870339</t>
+          <t>868958</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25560</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51117</t>
+          <t>49535</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33729</t>
+          <t>32679</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61887</t>
+          <t>59654</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>65059</t>
+          <t>66313</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102151</t>
+          <t>103663</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27332</t>
+          <t>27619</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33544</t>
+          <t>31330</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26281</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52198</t>
+          <t>52678</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>283736</t>
+          <t>283946</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>307132</t>
+          <t>305993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>319300</t>
+          <t>319288</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>342325</t>
+          <t>343181</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>609137</t>
+          <t>609334</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>644105</t>
+          <t>644130</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33927</t>
+          <t>33688</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>18617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>39419</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37166</t>
+          <t>36869</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67007</t>
+          <t>65923</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>19592</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>36569</t>
+          <t>35894</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>218510</t>
+          <t>220501</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>238066</t>
+          <t>237866</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>345451</t>
+          <t>345517</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>371612</t>
+          <t>371455</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>573315</t>
+          <t>572695</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>604087</t>
+          <t>605273</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28678</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15482</t>
+          <t>15803</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38170</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31868</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60146</t>
+          <t>59214</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15748</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23649</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2960710</t>
+          <t>2960910</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3031771</t>
+          <t>3034251</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3091658</t>
+          <t>3090149</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3168734</t>
+          <t>3173315</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6074932</t>
+          <t>6076321</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6182812</t>
+          <t>6178332</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>239058</t>
+          <t>240730</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>303879</t>
+          <t>303745</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>239618</t>
+          <t>238231</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>306473</t>
+          <t>309171</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>502946</t>
+          <t>500042</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>593440</t>
+          <t>588658</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>76785</t>
+          <t>78150</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>116673</t>
+          <t>117496</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>88339</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>131327</t>
+          <t>131241</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>174287</t>
+          <t>176594</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>233586</t>
+          <t>233361</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2023</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>358810</t>
+          <t>359579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>390199</t>
+          <t>390006</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>277653</t>
+          <t>277076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>301515</t>
+          <t>301270</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>643650</t>
+          <t>645897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>685185</t>
+          <t>686298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>31522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>15412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48477</t>
+          <t>49821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -12613,7 +12613,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>22288</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>29538</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>387103</t>
+          <t>387876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410511</t>
+          <t>411299</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>481955</t>
+          <t>483276</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502050</t>
+          <t>502628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>877252</t>
+          <t>876428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>908918</t>
+          <t>908250</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25876</t>
+          <t>25662</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30138</t>
+          <t>28817</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20542</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>45944</t>
+          <t>48107</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>19957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19663</t>
+          <t>19924</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>494044</t>
+          <t>492869</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>516093</t>
+          <t>516014</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>548154</t>
+          <t>549095</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>568472</t>
+          <t>567358</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1048845</t>
+          <t>1047835</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1079053</t>
+          <t>1078786</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31712</t>
+          <t>32307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14116</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>30467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13457,12 +13457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29938</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55135</t>
+          <t>56996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26294</t>
+          <t>25128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>830392</t>
+          <t>830033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>871155</t>
+          <t>871600</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>662876</t>
+          <t>663777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>683381</t>
+          <t>683946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1503556</t>
+          <t>1503883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1553532</t>
+          <t>1555296</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43295</t>
+          <t>44341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38342</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32747</t>
+          <t>32039</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72913</t>
+          <t>71739</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14434</t>
+          <t>14672</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>9315</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28404</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>519600</t>
+          <t>517996</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>538838</t>
+          <t>538133</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14221,12 +14221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>513550</t>
+          <t>513323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>527939</t>
+          <t>528090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1037808</t>
+          <t>1038021</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1062141</t>
+          <t>1063109</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29014</t>
+          <t>28718</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22835</t>
+          <t>22064</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26474</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46708</t>
+          <t>45591</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13337</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10057</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>24934</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>345352</t>
+          <t>345703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>358379</t>
+          <t>358764</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>571080</t>
+          <t>571565</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>599402</t>
+          <t>599315</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>924395</t>
+          <t>924235</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>957071</t>
+          <t>956219</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17364</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28568</t>
+          <t>28818</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39459</t>
+          <t>39657</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>8019</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>261470</t>
+          <t>262797</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>274613</t>
+          <t>274591</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>402871</t>
+          <t>402872</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>414270</t>
+          <t>413524</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>669554</t>
+          <t>669814</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>686180</t>
+          <t>686045</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16582</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15342</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30991</t>
+          <t>30592</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3258294</t>
+          <t>3259777</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3323429</t>
+          <t>3328401</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3508070</t>
+          <t>3507655</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3564220</t>
+          <t>3565796</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6777796</t>
+          <t>6780341</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6873882</t>
+          <t>6875701</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>88013</t>
+          <t>89749</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>142201</t>
+          <t>142670</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>99846</t>
+          <t>99628</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>145798</t>
+          <t>148752</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,12 +15737,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>201309</t>
+          <t>202757</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>278304</t>
+          <t>276070</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>32346</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>66559</t>
+          <t>64222</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>27981</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>52958</t>
+          <t>52988</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>66776</t>
+          <t>65921</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>109239</t>
+          <t>109232</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">

--- a/data/trans_orig/P05A04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A04-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>419350</t>
+          <t>419543</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>448585</t>
+          <t>448042</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>397972</t>
+          <t>399283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>424523</t>
+          <t>424587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>824871</t>
+          <t>826444</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>864697</t>
+          <t>864892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32833</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59724</t>
+          <t>58569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27463</t>
+          <t>26439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>48433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65658</t>
+          <t>66161</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100203</t>
+          <t>101512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14379</t>
+          <t>14217</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>31386</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>645667</t>
+          <t>648837</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>677932</t>
+          <t>677281</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>525203</t>
+          <t>527420</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>560612</t>
+          <t>559636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1182833</t>
+          <t>1180999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1230836</t>
+          <t>1227726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36951</t>
+          <t>37303</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64337</t>
+          <t>64426</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40316</t>
+          <t>41907</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72441</t>
+          <t>72293</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>86218</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>126123</t>
+          <t>127958</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,42 +1435,42 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17350</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9529</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26835</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17350</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9734</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>28163</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43485</t>
+          <t>42520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>529034</t>
+          <t>529196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>563734</t>
+          <t>565778</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>602204</t>
+          <t>599340</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>632442</t>
+          <t>631590</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1138444</t>
+          <t>1138507</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1188114</t>
+          <t>1189304</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61496</t>
+          <t>59638</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93806</t>
+          <t>93814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43542</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71537</t>
+          <t>73177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110462</t>
+          <t>111394</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158739</t>
+          <t>155368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20145</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,49 +1886,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>12820</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6702</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>21824</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>3,18%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>12820</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>7024</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>20833</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>23</t>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34986</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>452385</t>
+          <t>452690</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>478301</t>
+          <t>479289</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>436712</t>
+          <t>435488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>464829</t>
+          <t>465088</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>897088</t>
+          <t>897618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>935467</t>
+          <t>936409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26715</t>
+          <t>26614</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50025</t>
+          <t>50888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65076</t>
+          <t>65481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73602</t>
+          <t>71976</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109493</t>
+          <t>107558</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>18404</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,82 +2342,82 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>8205</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4021</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>16374</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>19095</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>11993</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>29737</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>8205</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4019</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>15190</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>19095</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>11857</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>29418</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>315475</t>
+          <t>312642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>341108</t>
+          <t>340884</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>344383</t>
+          <t>342520</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368836</t>
+          <t>368175</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>665943</t>
+          <t>666643</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>701697</t>
+          <t>703622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33327</t>
+          <t>32688</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57337</t>
+          <t>59330</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>20219</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41029</t>
+          <t>41705</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59332</t>
+          <t>58227</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92801</t>
+          <t>92129</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23034</t>
+          <t>23376</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32681</t>
+          <t>33439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>253962</t>
+          <t>254204</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>272700</t>
+          <t>274059</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>295254</t>
+          <t>297214</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>316580</t>
+          <t>317556</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>556741</t>
+          <t>558153</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>584931</t>
+          <t>585922</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>30175</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>18570</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39205</t>
+          <t>37756</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,47 +3176,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>49078</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>37437</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>63083</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>5,92%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>49078</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>37441</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>62382</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>181267</t>
+          <t>180608</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>195923</t>
+          <t>195967</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>280954</t>
+          <t>282314</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>306113</t>
+          <t>306021</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>470423</t>
+          <t>470513</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>497885</t>
+          <t>496984</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23732</t>
+          <t>24322</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21239</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45693</t>
+          <t>44413</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>35966</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62135</t>
+          <t>61503</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2859621</t>
+          <t>2860945</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2929945</t>
+          <t>2930565</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2949403</t>
+          <t>2948078</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3023021</t>
+          <t>3020706</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5833430</t>
+          <t>5832637</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5931113</t>
+          <t>5933824</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>256541</t>
+          <t>259641</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>326232</t>
+          <t>322953</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>256036</t>
+          <t>255920</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>321217</t>
+          <t>321049</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>533690</t>
+          <t>529305</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>626340</t>
+          <t>622290</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>43623</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>77251</t>
+          <t>73968</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>56876</t>
+          <t>58299</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>90920</t>
+          <t>93521</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>109209</t>
+          <t>108198</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>154712</t>
+          <t>154413</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>395629</t>
+          <t>393775</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>417598</t>
+          <t>417518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>388519</t>
+          <t>389902</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>409490</t>
+          <t>408653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>791922</t>
+          <t>790757</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>821182</t>
+          <t>821476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44892</t>
+          <t>46256</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>29073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39346</t>
+          <t>39322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67009</t>
+          <t>68378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14028</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>609078</t>
+          <t>611064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>640031</t>
+          <t>640822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>535230</t>
+          <t>534108</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>563726</t>
+          <t>563330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1153361</t>
+          <t>1154702</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1196712</t>
+          <t>1195046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>28364</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55614</t>
+          <t>54909</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32654</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58693</t>
+          <t>59888</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66711</t>
+          <t>67534</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>105926</t>
+          <t>105214</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25889</t>
+          <t>25846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18202</t>
+          <t>19062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>39864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>581071</t>
+          <t>583043</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>616371</t>
+          <t>617078</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>621555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>652571</t>
+          <t>652873</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1216474</t>
+          <t>1213713</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1263214</t>
+          <t>1261008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42991</t>
+          <t>43421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71830</t>
+          <t>73450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>36881</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64250</t>
+          <t>65368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85895</t>
+          <t>85684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126115</t>
+          <t>127486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32199</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21910</t>
+          <t>21909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46175</t>
+          <t>47639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>531602</t>
+          <t>531325</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>564827</t>
+          <t>565398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>534879</t>
+          <t>535430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>564770</t>
+          <t>565242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1077599</t>
+          <t>1076467</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1122939</t>
+          <t>1121160</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35105</t>
+          <t>35367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64622</t>
+          <t>63822</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34385</t>
+          <t>35211</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62978</t>
+          <t>63062</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77588</t>
+          <t>76348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>116524</t>
+          <t>115706</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18190</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39893</t>
+          <t>40418</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>389446</t>
+          <t>391025</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>411693</t>
+          <t>411592</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>384889</t>
+          <t>385964</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>412404</t>
+          <t>413313</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>784438</t>
+          <t>786720</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>819075</t>
+          <t>817681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>13588</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>32748</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22604</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44559</t>
+          <t>45228</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>40716</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>69853</t>
+          <t>70101</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21231</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>25539</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>270087</t>
+          <t>268905</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>289957</t>
+          <t>289154</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>313556</t>
+          <t>314232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>332733</t>
+          <t>332629</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>588729</t>
+          <t>589926</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>617326</t>
+          <t>617995</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29081</t>
+          <t>29727</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29821</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28196</t>
+          <t>28245</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52537</t>
+          <t>53890</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15131</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>21604</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>225468</t>
+          <t>224537</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>240371</t>
+          <t>240258</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>342412</t>
+          <t>340772</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>365206</t>
+          <t>364631</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>572061</t>
+          <t>573001</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>601528</t>
+          <t>601628</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19966</t>
+          <t>20507</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42083</t>
+          <t>43765</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28061</t>
+          <t>27937</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>55037</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>11550</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3063336</t>
+          <t>3064807</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3131206</t>
+          <t>3134388</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3184442</t>
+          <t>3186366</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3254864</t>
+          <t>3256922</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6271385</t>
+          <t>6271941</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6367958</t>
+          <t>6366356</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>199682</t>
+          <t>200100</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>264374</t>
+          <t>259272</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>210645</t>
+          <t>213410</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>273717</t>
+          <t>273167</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>433378</t>
+          <t>431257</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>55021</t>
+          <t>53481</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>89764</t>
+          <t>89029</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>45758</t>
+          <t>45780</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>79311</t>
+          <t>78541</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>109538</t>
+          <t>108450</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>156782</t>
+          <t>158076</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>362363</t>
+          <t>363222</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>388394</t>
+          <t>388060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>332202</t>
+          <t>332438</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>358236</t>
+          <t>357511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>704831</t>
+          <t>703715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>740556</t>
+          <t>740719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46868</t>
+          <t>47088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50087</t>
+          <t>50095</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55015</t>
+          <t>54189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87564</t>
+          <t>86751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16938</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493013</t>
+          <t>493660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>526710</t>
+          <t>526716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485082</t>
+          <t>483130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512286</t>
+          <t>512648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>986181</t>
+          <t>988635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1029305</t>
+          <t>1030385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,9%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41292</t>
+          <t>40110</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70817</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30499</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54288</t>
+          <t>56170</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79240</t>
+          <t>78357</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>114831</t>
+          <t>115154</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>28965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31070</t>
+          <t>31219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28300</t>
+          <t>28157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53861</t>
+          <t>53794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>586563</t>
+          <t>587076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>617301</t>
+          <t>617264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>576737</t>
+          <t>575774</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>605656</t>
+          <t>605858</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1174347</t>
+          <t>1174601</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1217089</t>
+          <t>1217146</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37953</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>65938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34697</t>
+          <t>34182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60076</t>
+          <t>60619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78171</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116326</t>
+          <t>117391</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19041</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18729</t>
+          <t>19287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>41410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>541146</t>
+          <t>539636</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>576279</t>
+          <t>574763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>557362</t>
+          <t>557713</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>587666</t>
+          <t>589375</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1108465</t>
+          <t>1107274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1152572</t>
+          <t>1155970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40548</t>
+          <t>41282</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69787</t>
+          <t>71892</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34873</t>
+          <t>34712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61801</t>
+          <t>62431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84661</t>
+          <t>83025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123042</t>
+          <t>124969</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34035</t>
+          <t>33655</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12675</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30030</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30767</t>
+          <t>30661</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59213</t>
+          <t>58454</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>405140</t>
+          <t>404847</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>433193</t>
+          <t>434256</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>411676</t>
+          <t>412765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>444509</t>
+          <t>443894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>825305</t>
+          <t>826653</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>868958</t>
+          <t>870130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25813</t>
+          <t>25532</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49535</t>
+          <t>49868</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32679</t>
+          <t>32871</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59654</t>
+          <t>60017</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>66313</t>
+          <t>64722</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>103663</t>
+          <t>102096</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27619</t>
+          <t>28181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>12312</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31330</t>
+          <t>32272</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27192</t>
+          <t>25901</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52678</t>
+          <t>51496</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>283946</t>
+          <t>283671</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>305993</t>
+          <t>306291</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>319288</t>
+          <t>319378</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>343181</t>
+          <t>343155</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>609334</t>
+          <t>609457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>644130</t>
+          <t>643229</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14517</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33688</t>
+          <t>34913</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39419</t>
+          <t>38550</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36869</t>
+          <t>37613</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65923</t>
+          <t>65973</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>19989</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15874</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35894</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>220501</t>
+          <t>218899</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>237866</t>
+          <t>238055</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>345517</t>
+          <t>345565</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>371455</t>
+          <t>370926</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>572695</t>
+          <t>573537</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>605273</t>
+          <t>604601</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28585</t>
+          <t>29401</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39616</t>
+          <t>37767</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32139</t>
+          <t>32439</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59214</t>
+          <t>58427</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>15633</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23449</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2960910</t>
+          <t>2959044</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3034251</t>
+          <t>3032837</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3090149</t>
+          <t>3093712</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3173315</t>
+          <t>3169131</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6076321</t>
+          <t>6076649</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6178332</t>
+          <t>6180294</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240730</t>
+          <t>240699</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>303745</t>
+          <t>308118</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>238231</t>
+          <t>239705</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>309171</t>
+          <t>303774</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>500042</t>
+          <t>497706</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>588658</t>
+          <t>584045</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>78150</t>
+          <t>76059</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>117496</t>
+          <t>114556</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>90068</t>
+          <t>88252</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>131241</t>
+          <t>129105</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>176594</t>
+          <t>174575</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>233361</t>
+          <t>234176</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -12377,27 +12377,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>378157</t>
+          <t>386004</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>359579</t>
+          <t>367614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>390006</t>
+          <t>397598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>291860</t>
+          <t>333624</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>277076</t>
+          <t>315421</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>301270</t>
+          <t>344575</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>670017</t>
+          <t>719629</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>645897</t>
+          <t>692671</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>686298</t>
+          <t>734692</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -12490,32 +12490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31522</t>
+          <t>33578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,32 +12525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26447</t>
+          <t>33125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>32831</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15412</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49821</t>
+          <t>57915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -12613,12 +12613,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22288</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12638,32 +12638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20029</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,32 +12673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29538</t>
+          <t>27525</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>311770</t>
+          <t>357121</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>311770</t>
+          <t>357121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>311770</t>
+          <t>357121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>711757</t>
+          <t>764915</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>711757</t>
+          <t>764915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>711757</t>
+          <t>764915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>401249</t>
+          <t>450087</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>387876</t>
+          <t>433390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411299</t>
+          <t>460761</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>493707</t>
+          <t>481656</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483276</t>
+          <t>471088</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502628</t>
+          <t>489756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>894956</t>
+          <t>931743</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>876428</t>
+          <t>914979</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>908250</t>
+          <t>945436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25662</t>
+          <t>32955</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,32 +12981,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18386</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28817</t>
+          <t>30645</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13016,32 +13016,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>32389</t>
+          <t>38297</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21304</t>
+          <t>26115</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48107</t>
+          <t>53900</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13129,32 +13129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>22543</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,32 +13289,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>506788</t>
+          <t>584677</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>492869</t>
+          <t>570119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>516014</t>
+          <t>595981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13324,32 +13324,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>558454</t>
+          <t>585407</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>549095</t>
+          <t>575398</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>567358</t>
+          <t>594651</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1065243</t>
+          <t>1170084</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1047835</t>
+          <t>1152833</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078786</t>
+          <t>1183234</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>14672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32307</t>
+          <t>37169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21755</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30467</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,32 +13472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41553</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30632</t>
+          <t>37502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56996</t>
+          <t>63942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -13515,32 +13515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>17555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,32 +13550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>16254</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>24800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>587535</t>
+          <t>618579</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>587535</t>
+          <t>618579</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>587535</t>
+          <t>618579</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1122525</t>
+          <t>1236034</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1122525</t>
+          <t>1236034</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1122525</t>
+          <t>1236034</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>850647</t>
+          <t>658880</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>830033</t>
+          <t>644832</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>871600</t>
+          <t>669937</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>674163</t>
+          <t>695960</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>663777</t>
+          <t>685649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>683946</t>
+          <t>705240</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1524810</t>
+          <t>1354840</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1503883</t>
+          <t>1335708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1555296</t>
+          <t>1368725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26227</t>
+          <t>28372</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44341</t>
+          <t>40728</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28120</t>
+          <t>29549</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>21457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37440</t>
+          <t>40085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>54347</t>
+          <t>57922</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32039</t>
+          <t>46052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71739</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19671</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>21886</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28127</t>
+          <t>31597</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>711068</t>
+          <t>734965</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>711068</t>
+          <t>734965</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>711068</t>
+          <t>734965</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1597850</t>
+          <t>1434648</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1597850</t>
+          <t>1434648</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1597850</t>
+          <t>1434648</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>529827</t>
+          <t>577335</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>517996</t>
+          <t>565379</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>538133</t>
+          <t>586346</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>521387</t>
+          <t>580645</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>513323</t>
+          <t>572466</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>528090</t>
+          <t>587016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1051214</t>
+          <t>1157980</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1038021</t>
+          <t>1145763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1063109</t>
+          <t>1169276</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -14314,102 +14314,102 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>19868</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28718</t>
+          <t>28868</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>16745</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>11891</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>23345</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>36613</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>27298</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>46531</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>2,25%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>15645</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>10716</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>22064</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>34992</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>25643</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>45591</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16604</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,32 +14462,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7687</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>16760</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10139</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24934</t>
+          <t>25167</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>557901</t>
+          <t>606011</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>557901</t>
+          <t>606011</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>557901</t>
+          <t>606011</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>544719</t>
+          <t>605342</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>544719</t>
+          <t>605342</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>544719</t>
+          <t>605342</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1102620</t>
+          <t>1211353</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1102620</t>
+          <t>1211353</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1102620</t>
+          <t>1211353</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,27 +14657,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>353076</t>
+          <t>390932</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>345703</t>
+          <t>382544</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>358764</t>
+          <t>396707</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>585735</t>
+          <t>414392</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>571565</t>
+          <t>406826</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>599315</t>
+          <t>420154</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>938811</t>
+          <t>805324</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>924235</t>
+          <t>794269</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>956219</t>
+          <t>814085</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>11902</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28818</t>
+          <t>24098</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>27812</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39657</t>
+          <t>38881</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10151</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>15656</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>437867</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>437867</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>437867</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>975357</t>
+          <t>844947</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>975357</t>
+          <t>844947</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>975357</t>
+          <t>844947</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>269600</t>
+          <t>295390</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>262797</t>
+          <t>286959</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>274591</t>
+          <t>300924</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>409236</t>
+          <t>445702</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>402872</t>
+          <t>438446</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>413524</t>
+          <t>450745</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>678836</t>
+          <t>741092</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>669814</t>
+          <t>730489</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>686045</t>
+          <t>749279</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>22064</t>
+          <t>24347</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30592</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -15339,32 +15339,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>461657</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>461657</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>461657</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>706141</t>
+          <t>771855</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>706141</t>
+          <t>771855</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>706141</t>
+          <t>771855</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3289346</t>
+          <t>3343306</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3259777</t>
+          <t>3314395</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3328401</t>
+          <t>3370911</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3534542</t>
+          <t>3537386</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3507655</t>
+          <t>3512316</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3565796</t>
+          <t>3559969</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>6823887</t>
+          <t>6880691</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6780341</t>
+          <t>6839413</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6875701</t>
+          <t>6917096</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>117144</t>
+          <t>131360</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>89749</t>
+          <t>108145</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>142670</t>
+          <t>156622</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>124239</t>
+          <t>138125</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>99628</t>
+          <t>117681</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>148752</t>
+          <t>161519</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>241383</t>
+          <t>269485</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>202757</t>
+          <t>237020</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>276070</t>
+          <t>302941</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>47642</t>
+          <t>50445</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31375</t>
+          <t>36756</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>64222</t>
+          <t>70019</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>38978</t>
+          <t>41752</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>30891</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>52988</t>
+          <t>54542</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>86620</t>
+          <t>92197</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>65921</t>
+          <t>74036</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>109232</t>
+          <t>113622</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3454132</t>
+          <t>3525111</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3454132</t>
+          <t>3525111</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3454132</t>
+          <t>3525111</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3697759</t>
+          <t>3717263</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3697759</t>
+          <t>3717263</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3697759</t>
+          <t>3717263</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7151890</t>
+          <t>7242373</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7151890</t>
+          <t>7242373</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7151890</t>
+          <t>7242373</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
